--- a/TeplosilaWeb/Content/properties/gtrv.xlsx
+++ b/TeplosilaWeb/Content/properties/gtrv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pge27\OneDrive\Рабочий стол\TeploSilaWeb\TeplosilaWeb\Content\properties\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C2F811A-2F60-4F32-85D3-0DE471A431E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2EFED6-FDD4-4B32-A9E3-2AFF1B28536E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5025" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -109,15 +109,6 @@
     <t>TSL-2200-40-2AR-24-IP67</t>
   </si>
   <si>
-    <t>TSL-1600-25-2-24-IP67</t>
-  </si>
-  <si>
-    <t>TSL-2200-40-2-24-IP67</t>
-  </si>
-  <si>
-    <t>TSL-3000-60-2-24-IP67</t>
-  </si>
-  <si>
     <t>TSL-1600-25-2T-230-IP67</t>
   </si>
   <si>
@@ -125,6 +116,15 @@
   </si>
   <si>
     <t>TSL-3000-60-2T-230-IP67</t>
+  </si>
+  <si>
+    <t>TSL-1600-25-2М-24-IP67</t>
+  </si>
+  <si>
+    <t>TSL-2200-40-2М-24-IP67</t>
+  </si>
+  <si>
+    <t>TSL-3000-60-2М-24-IP67</t>
   </si>
 </sst>
 </file>
@@ -830,7 +830,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C9" s="5">
         <v>305</v>
@@ -862,7 +862,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" s="9">
         <v>305</v>
@@ -1106,7 +1106,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -1132,7 +1132,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -1314,7 +1314,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -1340,7 +1340,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -1502,7 +1502,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C33" s="5">
         <v>6.2</v>
@@ -1534,7 +1534,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C34" s="9">
         <v>6.2</v>
@@ -1778,7 +1778,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
@@ -1804,7 +1804,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
@@ -1986,7 +1986,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
@@ -2012,7 +2012,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
